--- a/JsonConverter/ExcelFiles/WJWave.xlsx
+++ b/JsonConverter/ExcelFiles/WJWave.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\OZ_Project\WJMainProject2D\JsonConverter\ExcelFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A6D090D0-F1CB-4F80-8422-FBD593FA3D5D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C3E15976-2F38-455B-ACB0-EE36E8F4893A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="975" yWindow="3045" windowWidth="21270" windowHeight="11145" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4620" yWindow="2040" windowWidth="17010" windowHeight="11145" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="WJTable_Wave" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="25">
   <si>
     <t>(name)</t>
   </si>
@@ -86,6 +86,38 @@
   </si>
   <si>
     <t>WaveEnemy_1_2</t>
+  </si>
+  <si>
+    <t>Wave_2_1</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>Wave_2_2</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>스테이지 2-1 웨이브</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>스테이지 2-2 웨이브</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>Wave_3_1</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>Wave_3_2</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>스테이지 3-1 웨이브</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>스테이지 3-2 웨이브</t>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -198,7 +230,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -208,9 +240,6 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -534,71 +563,111 @@
       <c r="H5" s="3"/>
     </row>
     <row r="6" spans="1:8" ht="15.75" customHeight="1">
-      <c r="A6" s="4"/>
-      <c r="B6" s="5"/>
-      <c r="C6" s="5"/>
-      <c r="D6" s="5"/>
-      <c r="E6" s="5"/>
+      <c r="A6" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="C6" s="4">
+        <v>1</v>
+      </c>
+      <c r="D6" s="4">
+        <v>10</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>15</v>
+      </c>
       <c r="F6" s="3"/>
       <c r="G6" s="3"/>
       <c r="H6" s="3"/>
     </row>
     <row r="7" spans="1:8" ht="15.75" customHeight="1">
-      <c r="A7" s="4"/>
-      <c r="B7" s="4"/>
-      <c r="C7" s="4"/>
-      <c r="D7" s="4"/>
-      <c r="E7" s="4"/>
+      <c r="A7" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="C7" s="4">
+        <v>2</v>
+      </c>
+      <c r="D7" s="4">
+        <v>5</v>
+      </c>
+      <c r="E7" s="4" t="s">
+        <v>16</v>
+      </c>
       <c r="F7" s="3"/>
       <c r="G7" s="3"/>
       <c r="H7" s="3"/>
     </row>
     <row r="8" spans="1:8" ht="15.75" customHeight="1">
-      <c r="A8" s="6"/>
-      <c r="B8" s="6"/>
-      <c r="C8" s="6"/>
-      <c r="D8" s="6"/>
-      <c r="E8" s="6"/>
+      <c r="A8" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="C8" s="4">
+        <v>1</v>
+      </c>
+      <c r="D8" s="4">
+        <v>10</v>
+      </c>
+      <c r="E8" s="4" t="s">
+        <v>15</v>
+      </c>
       <c r="F8" s="3"/>
       <c r="G8" s="3"/>
       <c r="H8" s="3"/>
     </row>
     <row r="9" spans="1:8" ht="15.75" customHeight="1">
-      <c r="A9" s="6"/>
-      <c r="B9" s="6"/>
-      <c r="C9" s="6"/>
-      <c r="D9" s="6"/>
-      <c r="E9" s="6"/>
+      <c r="A9" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="C9" s="4">
+        <v>2</v>
+      </c>
+      <c r="D9" s="4">
+        <v>5</v>
+      </c>
+      <c r="E9" s="4" t="s">
+        <v>16</v>
+      </c>
       <c r="F9" s="3"/>
       <c r="G9" s="3"/>
       <c r="H9" s="3"/>
     </row>
     <row r="10" spans="1:8" ht="15.75" customHeight="1">
-      <c r="A10" s="7"/>
-      <c r="B10" s="7"/>
-      <c r="C10" s="7"/>
-      <c r="D10" s="7"/>
-      <c r="E10" s="7"/>
+      <c r="A10" s="6"/>
+      <c r="B10" s="6"/>
+      <c r="C10" s="6"/>
+      <c r="D10" s="6"/>
+      <c r="E10" s="6"/>
       <c r="F10" s="3"/>
       <c r="G10" s="3"/>
       <c r="H10" s="3"/>
     </row>
     <row r="11" spans="1:8" ht="15.75" customHeight="1">
-      <c r="A11" s="7"/>
-      <c r="B11" s="7"/>
-      <c r="C11" s="7"/>
-      <c r="D11" s="7"/>
-      <c r="E11" s="7"/>
+      <c r="A11" s="6"/>
+      <c r="B11" s="6"/>
+      <c r="C11" s="6"/>
+      <c r="D11" s="6"/>
+      <c r="E11" s="6"/>
       <c r="F11" s="3"/>
       <c r="G11" s="3"/>
       <c r="H11" s="3"/>
     </row>
     <row r="12" spans="1:8" ht="15.75" customHeight="1">
-      <c r="A12" s="6"/>
-      <c r="B12" s="6"/>
-      <c r="C12" s="6"/>
-      <c r="D12" s="6"/>
-      <c r="E12" s="6"/>
+      <c r="A12" s="5"/>
+      <c r="B12" s="5"/>
+      <c r="C12" s="5"/>
+      <c r="D12" s="5"/>
+      <c r="E12" s="5"/>
       <c r="F12" s="3"/>
       <c r="G12" s="3"/>
       <c r="H12" s="3"/>
@@ -614,164 +683,164 @@
       <c r="H13" s="3"/>
     </row>
     <row r="14" spans="1:8" ht="15.75" customHeight="1">
-      <c r="A14" s="7"/>
-      <c r="B14" s="7"/>
-      <c r="C14" s="7"/>
-      <c r="D14" s="7"/>
-      <c r="E14" s="7"/>
+      <c r="A14" s="6"/>
+      <c r="B14" s="6"/>
+      <c r="C14" s="6"/>
+      <c r="D14" s="6"/>
+      <c r="E14" s="6"/>
       <c r="F14" s="3"/>
       <c r="G14" s="3"/>
       <c r="H14" s="3"/>
     </row>
     <row r="15" spans="1:8" ht="15.75" customHeight="1">
-      <c r="A15" s="7"/>
-      <c r="B15" s="7"/>
-      <c r="C15" s="7"/>
-      <c r="D15" s="7"/>
-      <c r="E15" s="7"/>
+      <c r="A15" s="6"/>
+      <c r="B15" s="6"/>
+      <c r="C15" s="6"/>
+      <c r="D15" s="6"/>
+      <c r="E15" s="6"/>
       <c r="F15" s="3"/>
       <c r="G15" s="3"/>
       <c r="H15" s="3"/>
     </row>
     <row r="16" spans="1:8" ht="15.75" customHeight="1">
-      <c r="A16" s="8"/>
-      <c r="B16" s="8"/>
-      <c r="C16" s="8"/>
-      <c r="D16" s="8"/>
-      <c r="E16" s="8"/>
+      <c r="A16" s="7"/>
+      <c r="B16" s="7"/>
+      <c r="C16" s="7"/>
+      <c r="D16" s="7"/>
+      <c r="E16" s="7"/>
     </row>
     <row r="17" spans="1:5" ht="15.75" customHeight="1">
-      <c r="A17" s="9"/>
-      <c r="B17" s="9"/>
-      <c r="C17" s="9"/>
-      <c r="D17" s="9"/>
-      <c r="E17" s="9"/>
+      <c r="A17" s="8"/>
+      <c r="B17" s="8"/>
+      <c r="C17" s="8"/>
+      <c r="D17" s="8"/>
+      <c r="E17" s="8"/>
     </row>
     <row r="18" spans="1:5" ht="15.75" customHeight="1">
-      <c r="A18" s="9"/>
-      <c r="B18" s="9"/>
-      <c r="C18" s="9"/>
-      <c r="D18" s="9"/>
-      <c r="E18" s="9"/>
+      <c r="A18" s="8"/>
+      <c r="B18" s="8"/>
+      <c r="C18" s="8"/>
+      <c r="D18" s="8"/>
+      <c r="E18" s="8"/>
     </row>
     <row r="19" spans="1:5" ht="15.75" customHeight="1">
-      <c r="A19" s="9"/>
-      <c r="B19" s="9"/>
-      <c r="C19" s="9"/>
-      <c r="D19" s="9"/>
-      <c r="E19" s="9"/>
+      <c r="A19" s="8"/>
+      <c r="B19" s="8"/>
+      <c r="C19" s="8"/>
+      <c r="D19" s="8"/>
+      <c r="E19" s="8"/>
     </row>
     <row r="20" spans="1:5" ht="15.75" customHeight="1">
-      <c r="A20" s="9"/>
-      <c r="B20" s="9"/>
-      <c r="C20" s="9"/>
-      <c r="D20" s="9"/>
-      <c r="E20" s="9"/>
+      <c r="A20" s="8"/>
+      <c r="B20" s="8"/>
+      <c r="C20" s="8"/>
+      <c r="D20" s="8"/>
+      <c r="E20" s="8"/>
     </row>
     <row r="21" spans="1:5" ht="15.75" customHeight="1">
-      <c r="A21" s="9"/>
-      <c r="B21" s="9"/>
-      <c r="C21" s="9"/>
-      <c r="D21" s="9"/>
-      <c r="E21" s="9"/>
+      <c r="A21" s="8"/>
+      <c r="B21" s="8"/>
+      <c r="C21" s="8"/>
+      <c r="D21" s="8"/>
+      <c r="E21" s="8"/>
     </row>
     <row r="22" spans="1:5" ht="15.75" customHeight="1">
-      <c r="A22" s="9"/>
-      <c r="B22" s="9"/>
-      <c r="C22" s="9"/>
-      <c r="D22" s="9"/>
-      <c r="E22" s="9"/>
+      <c r="A22" s="8"/>
+      <c r="B22" s="8"/>
+      <c r="C22" s="8"/>
+      <c r="D22" s="8"/>
+      <c r="E22" s="8"/>
     </row>
     <row r="23" spans="1:5" ht="15.75" customHeight="1">
-      <c r="A23" s="9"/>
-      <c r="B23" s="9"/>
-      <c r="C23" s="9"/>
-      <c r="D23" s="9"/>
-      <c r="E23" s="9"/>
+      <c r="A23" s="8"/>
+      <c r="B23" s="8"/>
+      <c r="C23" s="8"/>
+      <c r="D23" s="8"/>
+      <c r="E23" s="8"/>
     </row>
     <row r="24" spans="1:5" ht="15.75" customHeight="1">
-      <c r="A24" s="9"/>
-      <c r="B24" s="9"/>
-      <c r="C24" s="9"/>
-      <c r="D24" s="9"/>
-      <c r="E24" s="9"/>
+      <c r="A24" s="8"/>
+      <c r="B24" s="8"/>
+      <c r="C24" s="8"/>
+      <c r="D24" s="8"/>
+      <c r="E24" s="8"/>
     </row>
     <row r="25" spans="1:5" ht="15.75" customHeight="1">
-      <c r="A25" s="9"/>
-      <c r="B25" s="9"/>
-      <c r="C25" s="9"/>
-      <c r="D25" s="9"/>
-      <c r="E25" s="9"/>
+      <c r="A25" s="8"/>
+      <c r="B25" s="8"/>
+      <c r="C25" s="8"/>
+      <c r="D25" s="8"/>
+      <c r="E25" s="8"/>
     </row>
     <row r="26" spans="1:5" ht="15.75" customHeight="1">
-      <c r="A26" s="10"/>
-      <c r="B26" s="10"/>
-      <c r="C26" s="10"/>
-      <c r="D26" s="10"/>
-      <c r="E26" s="10"/>
+      <c r="A26" s="9"/>
+      <c r="B26" s="9"/>
+      <c r="C26" s="9"/>
+      <c r="D26" s="9"/>
+      <c r="E26" s="9"/>
     </row>
     <row r="27" spans="1:5" ht="15.75" customHeight="1">
-      <c r="A27" s="10"/>
-      <c r="B27" s="10"/>
-      <c r="C27" s="10"/>
-      <c r="D27" s="10"/>
-      <c r="E27" s="10"/>
+      <c r="A27" s="9"/>
+      <c r="B27" s="9"/>
+      <c r="C27" s="9"/>
+      <c r="D27" s="9"/>
+      <c r="E27" s="9"/>
     </row>
     <row r="28" spans="1:5" ht="15.75" customHeight="1">
-      <c r="A28" s="10"/>
-      <c r="B28" s="10"/>
-      <c r="C28" s="10"/>
-      <c r="D28" s="10"/>
-      <c r="E28" s="10"/>
+      <c r="A28" s="9"/>
+      <c r="B28" s="9"/>
+      <c r="C28" s="9"/>
+      <c r="D28" s="9"/>
+      <c r="E28" s="9"/>
     </row>
     <row r="29" spans="1:5" ht="15.75" customHeight="1">
-      <c r="A29" s="10"/>
-      <c r="B29" s="10"/>
-      <c r="C29" s="10"/>
-      <c r="D29" s="10"/>
-      <c r="E29" s="10"/>
+      <c r="A29" s="9"/>
+      <c r="B29" s="9"/>
+      <c r="C29" s="9"/>
+      <c r="D29" s="9"/>
+      <c r="E29" s="9"/>
     </row>
     <row r="30" spans="1:5" ht="15.75" customHeight="1">
-      <c r="A30" s="10"/>
-      <c r="B30" s="10"/>
-      <c r="C30" s="10"/>
-      <c r="D30" s="10"/>
-      <c r="E30" s="10"/>
+      <c r="A30" s="9"/>
+      <c r="B30" s="9"/>
+      <c r="C30" s="9"/>
+      <c r="D30" s="9"/>
+      <c r="E30" s="9"/>
     </row>
     <row r="31" spans="1:5" ht="15.75" customHeight="1">
-      <c r="A31" s="10"/>
-      <c r="B31" s="10"/>
-      <c r="C31" s="10"/>
-      <c r="D31" s="10"/>
-      <c r="E31" s="10"/>
+      <c r="A31" s="9"/>
+      <c r="B31" s="9"/>
+      <c r="C31" s="9"/>
+      <c r="D31" s="9"/>
+      <c r="E31" s="9"/>
     </row>
     <row r="32" spans="1:5" ht="15.75" customHeight="1">
-      <c r="A32" s="11"/>
-      <c r="B32" s="11"/>
-      <c r="C32" s="11"/>
-      <c r="D32" s="11"/>
-      <c r="E32" s="11"/>
+      <c r="A32" s="10"/>
+      <c r="B32" s="10"/>
+      <c r="C32" s="10"/>
+      <c r="D32" s="10"/>
+      <c r="E32" s="10"/>
     </row>
     <row r="33" spans="1:5" ht="15.75" customHeight="1">
-      <c r="A33" s="11"/>
-      <c r="B33" s="11"/>
-      <c r="C33" s="11"/>
-      <c r="D33" s="11"/>
-      <c r="E33" s="11"/>
+      <c r="A33" s="10"/>
+      <c r="B33" s="10"/>
+      <c r="C33" s="10"/>
+      <c r="D33" s="10"/>
+      <c r="E33" s="10"/>
     </row>
     <row r="34" spans="1:5" ht="15.75" customHeight="1">
-      <c r="A34" s="11"/>
-      <c r="B34" s="11"/>
-      <c r="C34" s="11"/>
-      <c r="D34" s="11"/>
-      <c r="E34" s="11"/>
+      <c r="A34" s="10"/>
+      <c r="B34" s="10"/>
+      <c r="C34" s="10"/>
+      <c r="D34" s="10"/>
+      <c r="E34" s="10"/>
     </row>
     <row r="35" spans="1:5" ht="15.75" customHeight="1">
-      <c r="A35" s="11"/>
-      <c r="B35" s="11"/>
-      <c r="C35" s="11"/>
-      <c r="D35" s="11"/>
-      <c r="E35" s="11"/>
+      <c r="A35" s="10"/>
+      <c r="B35" s="10"/>
+      <c r="C35" s="10"/>
+      <c r="D35" s="10"/>
+      <c r="E35" s="10"/>
     </row>
     <row r="36" spans="1:5" ht="15.75" customHeight="1"/>
     <row r="37" spans="1:5" ht="15.75" customHeight="1"/>

--- a/JsonConverter/ExcelFiles/WJWave.xlsx
+++ b/JsonConverter/ExcelFiles/WJWave.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\OZ_Project\WJMainProject2D\JsonConverter\ExcelFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C3E15976-2F38-455B-ACB0-EE36E8F4893A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B4B3AC37-5281-404B-8325-73F88142AC09}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4620" yWindow="2040" windowWidth="17010" windowHeight="11145" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2250" yWindow="3600" windowWidth="25365" windowHeight="11520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="WJTable_Wave" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="29">
   <si>
     <t>(name)</t>
   </si>
@@ -118,6 +118,18 @@
   <si>
     <t>스테이지 3-2 웨이브</t>
     <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>WaveEnemy_2_1</t>
+  </si>
+  <si>
+    <t>WaveEnemy_2_2</t>
+  </si>
+  <si>
+    <t>WaveEnemy_3_1</t>
+  </si>
+  <si>
+    <t>WaveEnemy_3_2</t>
   </si>
 </sst>
 </file>
@@ -533,7 +545,7 @@
         <v>1</v>
       </c>
       <c r="D4" s="4">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="E4" s="4" t="s">
         <v>15</v>
@@ -553,7 +565,7 @@
         <v>2</v>
       </c>
       <c r="D5" s="4">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="E5" s="4" t="s">
         <v>16</v>
@@ -573,10 +585,10 @@
         <v>1</v>
       </c>
       <c r="D6" s="4">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="F6" s="3"/>
       <c r="G6" s="3"/>
@@ -593,10 +605,10 @@
         <v>2</v>
       </c>
       <c r="D7" s="4">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="F7" s="3"/>
       <c r="G7" s="3"/>
@@ -613,10 +625,10 @@
         <v>1</v>
       </c>
       <c r="D8" s="4">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="F8" s="3"/>
       <c r="G8" s="3"/>
@@ -633,10 +645,10 @@
         <v>2</v>
       </c>
       <c r="D9" s="4">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="F9" s="3"/>
       <c r="G9" s="3"/>
